--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc552b6141752447e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89e919dae42b4457"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89e919dae42b4457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf08ff205f8dc4955"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf08ff205f8dc4955"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e6478bbb47a405b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e6478bbb47a405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb79a484489fe462a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb79a484489fe462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R494e6075ebb34bd3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R494e6075ebb34bd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ba1f94d413247ef"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ba1f94d413247ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bb0ff01d8b843d4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bb0ff01d8b843d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe6523105cea4ae9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe6523105cea4ae9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R800bd7830b2f4295"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R800bd7830b2f4295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3ec4de12b414c26"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_List/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3ec4de12b414c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R003d0891ea974a3a"/>
   </x:sheets>
 </x:workbook>
 </file>
